--- a/artfynd/A 22095-2026 artfynd.xlsx
+++ b/artfynd/A 22095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4177,6 +4177,137 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133679383</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57971</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>547591</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6322252</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22095-2026 artfynd.xlsx
+++ b/artfynd/A 22095-2026 artfynd.xlsx
@@ -4182,7 +4182,7 @@
         <v>133679383</v>
       </c>
       <c r="B29" t="n">
-        <v>57971</v>
+        <v>57978</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 22095-2026 artfynd.xlsx
+++ b/artfynd/A 22095-2026 artfynd.xlsx
@@ -4182,7 +4182,7 @@
         <v>133679383</v>
       </c>
       <c r="B29" t="n">
-        <v>57978</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 22095-2026 artfynd.xlsx
+++ b/artfynd/A 22095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118625538</v>
+        <v>128649231</v>
       </c>
       <c r="B2" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,32 +708,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossbergavägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547603</v>
+        <v>547626</v>
       </c>
       <c r="R2" t="n">
-        <v>6322361</v>
+        <v>6322276</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -807,37 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118752908</v>
+        <v>128649243</v>
       </c>
       <c r="B3" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,31 +827,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossbergavägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547603</v>
+        <v>547666</v>
       </c>
       <c r="R3" t="n">
-        <v>6322361</v>
+        <v>6322183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,22 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,6 +894,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -938,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120760787</v>
+        <v>128649252</v>
       </c>
       <c r="B4" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,39 +946,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellan sjöarna, Grytsjön, Kråksmåla, Sm</t>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547550</v>
+        <v>547635</v>
       </c>
       <c r="R4" t="n">
-        <v>6322439</v>
+        <v>6322185</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,6 +1013,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1074,37 +1032,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277437</v>
+        <v>128142667</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1117,14 +1070,10 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1134,17 +1083,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Flaten, Grönskåra, Sm</t>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547296</v>
+        <v>547532</v>
       </c>
       <c r="R5" t="n">
-        <v>6322838</v>
+        <v>6322396</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1168,22 +1117,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>upphittade fjädrar vid resterna av en tjädertupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128141763</v>
+        <v>128320969</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>56814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,53 +1175,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547550</v>
+        <v>547569</v>
       </c>
       <c r="R6" t="n">
-        <v>6322393</v>
+        <v>6322310</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1291,22 +1250,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1333,10 +1297,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128293181</v>
+        <v>128495912</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>56814</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,53 +1308,58 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547494</v>
+        <v>547248</v>
       </c>
       <c r="R7" t="n">
-        <v>6322776</v>
+        <v>6322812</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1414,22 +1383,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1456,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128293205</v>
+        <v>128495996</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>56814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,53 +1441,58 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547394</v>
+        <v>547473</v>
       </c>
       <c r="R8" t="n">
-        <v>6322764</v>
+        <v>6322552</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1537,22 +1516,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,10 +1563,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128293153</v>
+        <v>128628219</v>
       </c>
       <c r="B9" t="n">
-        <v>57876</v>
+        <v>56814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,53 +1574,58 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547760</v>
+        <v>547566</v>
       </c>
       <c r="R9" t="n">
-        <v>6322405</v>
+        <v>6322282</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1660,22 +1649,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1702,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128293162</v>
+        <v>128629307</v>
       </c>
       <c r="B10" t="n">
-        <v>57876</v>
+        <v>56814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,53 +1707,58 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547683</v>
+        <v>547578</v>
       </c>
       <c r="R10" t="n">
-        <v>6322521</v>
+        <v>6322251</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1783,22 +1782,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1825,32 +1829,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128320990</v>
+        <v>128629364</v>
       </c>
       <c r="B11" t="n">
-        <v>56605</v>
+        <v>56814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>100015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1881,10 +1885,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547569</v>
+        <v>547512</v>
       </c>
       <c r="R11" t="n">
-        <v>6322310</v>
+        <v>6322420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1911,17 +1915,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1931,7 +1935,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>wurb2024 AA-44 med Pettersson u384</t>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1958,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128320983</v>
+        <v>117944829</v>
       </c>
       <c r="B12" t="n">
-        <v>56600</v>
+        <v>56925</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,21 +1973,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100092</v>
+        <v>100045</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1991,13 +1995,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2005,22 +2012,22 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Lilla Flaten, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547569</v>
+        <v>547785</v>
       </c>
       <c r="R12" t="n">
-        <v>6322310</v>
+        <v>6322270</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2044,27 +2051,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>wurb2024 AA-44 med Pettersson u384</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,66 +2093,69 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128320969</v>
+        <v>118010575</v>
       </c>
       <c r="B13" t="n">
-        <v>56746</v>
+        <v>56925</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100015</v>
+        <v>100045</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Lilla Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547569</v>
+        <v>547783</v>
       </c>
       <c r="R13" t="n">
-        <v>6322310</v>
+        <v>6322252</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2177,27 +2182,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>wurb2024 AA-44 med Pettersson u384</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,78 +2212,81 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>Ulrike  Ahlert</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>Ulrike  Ahlert</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128320974</v>
+        <v>118207144</v>
       </c>
       <c r="B14" t="n">
-        <v>56586</v>
+        <v>56925</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>100045</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Lilla Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547569</v>
+        <v>547766</v>
       </c>
       <c r="R14" t="n">
-        <v>6322310</v>
+        <v>6322248</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2310,7 +2313,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2320,17 +2323,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>wurb2024 AA-44 med Pettersson u384</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2357,10 +2355,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128531054</v>
+        <v>118424097</v>
       </c>
       <c r="B15" t="n">
-        <v>56603</v>
+        <v>56925</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,35 +2366,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>100045</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2404,22 +2405,22 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Lilla Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547337</v>
+        <v>547775</v>
       </c>
       <c r="R15" t="n">
-        <v>6322798</v>
+        <v>6322263</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2443,27 +2444,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>wurb2024 ka-01 med Pettersson u384</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2490,10 +2486,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128531057</v>
+        <v>128801352</v>
       </c>
       <c r="B16" t="n">
-        <v>56610</v>
+        <v>57966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2501,16 +2497,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206002</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2523,13 +2519,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2537,22 +2536,22 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547337</v>
+        <v>547583</v>
       </c>
       <c r="R16" t="n">
-        <v>6322798</v>
+        <v>6322234</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2576,27 +2575,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>wurb2024 ka-01 med Pettersson u384</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2623,10 +2617,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128531047</v>
+        <v>133679383</v>
       </c>
       <c r="B17" t="n">
-        <v>56589</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,35 +2628,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2670,22 +2667,22 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547337</v>
+        <v>547591</v>
       </c>
       <c r="R17" t="n">
-        <v>6322798</v>
+        <v>6322252</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2709,27 +2706,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>wurb2024 ka-01 med Pettersson u384</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2756,14 +2748,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128626896</v>
+        <v>118752908</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2789,11 +2781,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2803,17 +2798,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Flaten, Grönskåra, Sm</t>
+          <t>Mossbergavägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547296</v>
+        <v>547603</v>
       </c>
       <c r="R18" t="n">
-        <v>6322838</v>
+        <v>6322361</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2837,22 +2832,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2879,44 +2874,47 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128626898</v>
+        <v>119186181</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2926,17 +2924,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
+          <t>Hygget Stora Flaten, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547471</v>
+        <v>547568</v>
       </c>
       <c r="R19" t="n">
-        <v>6322624</v>
+        <v>6322778</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2960,22 +2958,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3002,10 +3000,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128629349</v>
+        <v>128626896</v>
       </c>
       <c r="B20" t="n">
-        <v>56610</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3013,58 +3011,53 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Stora Flaten, Grönskåra, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547578</v>
+        <v>547296</v>
       </c>
       <c r="R20" t="n">
-        <v>6322251</v>
+        <v>6322838</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3088,27 +3081,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>wurb2024 ka-02 med Pettersson u384</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3135,10 +3123,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128649231</v>
+        <v>118171335</v>
       </c>
       <c r="B21" t="n">
-        <v>92168</v>
+        <v>57258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3146,45 +3134,58 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6031</v>
+        <v>100065</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Lilla Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547626</v>
+        <v>547759</v>
       </c>
       <c r="R21" t="n">
-        <v>6322276</v>
+        <v>6322228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3211,22 +3212,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3235,7 +3236,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3254,27 +3254,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128629342</v>
+        <v>118207210</v>
       </c>
       <c r="B22" t="n">
-        <v>56612</v>
+        <v>57258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206002</v>
+        <v>100065</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3284,39 +3284,42 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Lilla Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547578</v>
+        <v>547775</v>
       </c>
       <c r="R22" t="n">
-        <v>6322251</v>
+        <v>6322263</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3340,27 +3343,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>wurb2024 ka-02 med Pettersson u384</t>
+          <t>2 par tranor vid Lilla Flaten ikväll</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3387,10 +3390,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128629347</v>
+        <v>118568269</v>
       </c>
       <c r="B23" t="n">
-        <v>56605</v>
+        <v>57258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3398,21 +3401,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>100065</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3420,33 +3423,36 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Lilla Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547578</v>
+        <v>547766</v>
       </c>
       <c r="R23" t="n">
-        <v>6322251</v>
+        <v>6322248</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3473,27 +3479,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>wurb2024 ka-02 med Pettersson u384</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3520,10 +3521,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128629309</v>
+        <v>128627723</v>
       </c>
       <c r="B24" t="n">
-        <v>56591</v>
+        <v>56822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3531,26 +3532,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>100086</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dammfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis dasycneme</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(F.Boie, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3576,10 +3577,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547578</v>
+        <v>547248</v>
       </c>
       <c r="R24" t="n">
-        <v>6322251</v>
+        <v>6322812</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3611,7 +3612,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3626,7 +3627,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>wurb2024 ka-02 med Pettersson u384</t>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3653,27 +3654,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128629307</v>
+        <v>128320983</v>
       </c>
       <c r="B25" t="n">
-        <v>56746</v>
+        <v>56830</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3709,10 +3710,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547578</v>
+        <v>547569</v>
       </c>
       <c r="R25" t="n">
-        <v>6322251</v>
+        <v>6322310</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3739,17 +3740,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3759,7 +3760,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>wurb2024 ka-02 med Pettersson u384</t>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3786,49 +3787,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128801352</v>
+        <v>128495925</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>56830</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>100092</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3836,22 +3834,22 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547583</v>
+        <v>547248</v>
       </c>
       <c r="R26" t="n">
-        <v>6322234</v>
+        <v>6322812</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3875,22 +3873,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3917,10 +3920,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129545905</v>
+        <v>128531054</v>
       </c>
       <c r="B27" t="n">
-        <v>56927</v>
+        <v>56830</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3928,58 +3931,55 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100092</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547707</v>
+        <v>547337</v>
       </c>
       <c r="R27" t="n">
-        <v>6322242</v>
+        <v>6322798</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4006,22 +4006,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-01 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4048,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129545906</v>
+        <v>128628229</v>
       </c>
       <c r="B28" t="n">
-        <v>56927</v>
+        <v>56830</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4059,58 +4064,55 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100092</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547727</v>
+        <v>547566</v>
       </c>
       <c r="R28" t="n">
-        <v>6322462</v>
+        <v>6322282</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4137,22 +4139,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4179,49 +4186,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133679383</v>
+        <v>128629347</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>56830</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100048</v>
+        <v>100092</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4229,22 +4233,22 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547591</v>
+        <v>547578</v>
       </c>
       <c r="R29" t="n">
-        <v>6322252</v>
+        <v>6322251</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4268,22 +4272,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4307,6 +4316,3915 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128706528</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lille Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>547759</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6322226</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120760787</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mellan sjöarna, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>547550</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6322439</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121277437</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora Flaten, Grönskåra, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>547296</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6322838</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128142664</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>547532</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6322396</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>blev troligen tagen av en duvhök. Inga avbitna fjädrar.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129545905</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>547707</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6322242</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129545906</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>547727</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6322462</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118625538</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mossbergavägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>547603</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6322361</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128141758</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>547386</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6322716</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128141763</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>547550</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6322393</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128293153</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>547760</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6322405</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128293162</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>547683</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6322521</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128293181</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>547494</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6322776</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128293205</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>547394</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6322764</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128626898</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>547471</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6322624</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128320990</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>547569</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6322310</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128495958</v>
+      </c>
+      <c r="B45" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>547248</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6322812</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128628224</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>547566</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6322282</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128629349</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128629374</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>547512</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6322420</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128706517</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lille Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>547759</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6322226</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128320974</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>547569</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6322310</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128495915</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>547248</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6322812</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128496006</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>547473</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6322552</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128531047</v>
+      </c>
+      <c r="B53" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>547337</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6322798</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-01 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128628222</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>547566</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6322282</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128629309</v>
+      </c>
+      <c r="B55" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128629372</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>547512</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6322420</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128706470</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lille Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>547759</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6322226</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128531057</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>547337</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6322798</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-01 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128629342</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22095-2026 artfynd.xlsx
+++ b/artfynd/A 22095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128649231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128649243</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128649252</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1161,6 +1181,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128142667</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1294,6 +1319,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128320969</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1427,6 +1457,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495912</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1560,6 +1595,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495996</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1693,6 +1733,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128628219</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1826,6 +1871,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629307</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1959,6 +2009,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629364</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2090,6 +2145,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117944829</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2221,6 +2281,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118010575</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2352,6 +2417,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118207144</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2483,6 +2553,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118424097</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2614,6 +2689,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128801352</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2745,6 +2825,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133679383</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2871,6 +2956,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118752908</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2997,6 +3087,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186181</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3120,6 +3215,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626896</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3251,6 +3351,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118171335</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3387,6 +3492,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118207210</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3518,6 +3628,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568269</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3651,6 +3766,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627723</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3784,6 +3904,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128320983</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3917,6 +4042,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495925</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4050,6 +4180,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128531054</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4183,6 +4318,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128628229</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4316,6 +4456,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629347</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4449,6 +4594,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128706528</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4580,6 +4730,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120760787</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4711,6 +4866,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121277437</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4843,6 +5003,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128142664</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4974,6 +5139,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129545905</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5105,6 +5275,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129545906</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5232,6 +5407,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118625538</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5359,6 +5539,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128141758</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5482,6 +5667,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128141763</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5605,6 +5795,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128293153</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5728,6 +5923,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128293162</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5851,6 +6051,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128293181</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5974,6 +6179,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128293205</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6097,6 +6307,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626898</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6230,6 +6445,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128320990</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6363,6 +6583,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495958</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6496,6 +6721,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128628224</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6629,6 +6859,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629349</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6762,6 +6997,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629374</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6895,6 +7135,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128706517</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7028,6 +7273,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128320974</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7161,6 +7411,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495915</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7294,6 +7549,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128496006</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7427,6 +7687,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128531047</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7560,6 +7825,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128628222</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7693,6 +7963,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629309</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7826,6 +8101,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629372</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7959,6 +8239,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128706470</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8092,6 +8377,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128531057</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8225,8 +8515,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>